--- a/日常文件/execl模板下单/3.3V/新KEC upload order template(Multi-item single line) (12).xlsx
+++ b/日常文件/execl模板下单/3.3V/新KEC upload order template(Multi-item single line) (12).xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="869" uniqueCount="456">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="869" uniqueCount="457">
   <si>
     <t>Channel Code</t>
   </si>
@@ -427,85 +427,88 @@
     <t>Product 2 Spec</t>
   </si>
   <si>
+    <t>KEC-TESTGX</t>
+  </si>
+  <si>
+    <t>default</t>
+  </si>
+  <si>
+    <t>ITTEST202601070021</t>
+  </si>
+  <si>
+    <t>BACK</t>
+  </si>
+  <si>
+    <t>东莞市</t>
+  </si>
+  <si>
+    <t>KEC</t>
+  </si>
+  <si>
+    <t>CN</t>
+  </si>
+  <si>
+    <t>000000</t>
+  </si>
+  <si>
+    <t>tax_card</t>
+  </si>
+  <si>
+    <t>test123</t>
+  </si>
+  <si>
+    <t>IM3720001952</t>
+  </si>
+  <si>
+    <t>ES</t>
+  </si>
+  <si>
+    <t>我的小伙伴</t>
+  </si>
+  <si>
+    <t>ABC</t>
+  </si>
+  <si>
+    <t>PORCUNA</t>
+  </si>
+  <si>
+    <t>JAEN</t>
+  </si>
+  <si>
+    <t>TH</t>
+  </si>
+  <si>
+    <t>21000</t>
+  </si>
+  <si>
+    <t>passport</t>
+  </si>
+  <si>
+    <t>back</t>
+  </si>
+  <si>
+    <t>保税区</t>
+  </si>
+  <si>
+    <t>gd</t>
+  </si>
+  <si>
+    <t>sz</t>
+  </si>
+  <si>
+    <t>ft</t>
+  </si>
+  <si>
+    <t>CNY</t>
+  </si>
+  <si>
+    <t>PP</t>
+  </si>
+  <si>
+    <t>RETURN</t>
+  </si>
+  <si>
     <t>backtest</t>
-  </si>
-  <si>
-    <t>default</t>
-  </si>
-  <si>
-    <t>ITTEST20251-22</t>
-  </si>
-  <si>
-    <t>BACK</t>
-  </si>
-  <si>
-    <t>东莞市</t>
-  </si>
-  <si>
-    <t>KEC</t>
-  </si>
-  <si>
-    <t>CN</t>
-  </si>
-  <si>
-    <t>000000</t>
-  </si>
-  <si>
-    <t>tax_card</t>
-  </si>
-  <si>
-    <t>test123</t>
-  </si>
-  <si>
-    <t>IM3720001952</t>
-  </si>
-  <si>
-    <t>ES</t>
-  </si>
-  <si>
-    <t>我的小伙伴</t>
-  </si>
-  <si>
-    <t>ABC</t>
-  </si>
-  <si>
-    <t>PORCUNA</t>
-  </si>
-  <si>
-    <t>JAEN</t>
-  </si>
-  <si>
-    <t>TH</t>
-  </si>
-  <si>
-    <t>21000</t>
-  </si>
-  <si>
-    <t>passport</t>
-  </si>
-  <si>
-    <t>back</t>
-  </si>
-  <si>
-    <t>保税区</t>
-  </si>
-  <si>
-    <t>gd</t>
-  </si>
-  <si>
-    <t>sz</t>
-  </si>
-  <si>
-    <t>ft</t>
-  </si>
-  <si>
-    <t>CNY</t>
-  </si>
-  <si>
-    <t>PP</t>
-  </si>
-  <si>
-    <t>RETURN</t>
   </si>
   <si>
     <t>汽车速效镀膜剂液体喷雾</t>
@@ -3223,10 +3226,10 @@
         <v>12312313</v>
       </c>
       <c r="BZ2" s="2" t="s">
-        <v>131</v>
+        <v>158</v>
       </c>
       <c r="CA2" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="CD2" s="2">
         <v>9.81</v>
@@ -3282,20 +3285,15 @@
       <c r="D3" s="6"/>
       <c r="E3" s="7"/>
       <c r="F3" s="6"/>
-      <c r="G3"/>
       <c r="H3" s="3"/>
       <c r="I3" s="6"/>
       <c r="J3" s="5"/>
       <c r="K3" s="5"/>
       <c r="L3" s="5"/>
-      <c r="M3"/>
-      <c r="N3"/>
       <c r="O3" s="5"/>
-      <c r="P3"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
       <c r="S3" s="5"/>
-      <c r="T3"/>
       <c r="U3" s="3"/>
       <c r="V3" s="3"/>
       <c r="W3" s="3"/>
@@ -3307,26 +3305,14 @@
       <c r="AC3" s="5"/>
       <c r="AD3" s="5"/>
       <c r="AE3" s="5"/>
-      <c r="AF3"/>
-      <c r="AG3"/>
       <c r="AH3" s="5"/>
-      <c r="AI3"/>
       <c r="AJ3" s="5"/>
       <c r="AK3" s="5"/>
       <c r="AL3" s="5"/>
-      <c r="AM3"/>
       <c r="AN3" s="3"/>
       <c r="AO3" s="3"/>
       <c r="AP3" s="3"/>
-      <c r="AQ3"/>
       <c r="AR3" s="3"/>
-      <c r="AS3"/>
-      <c r="AT3"/>
-      <c r="AU3"/>
-      <c r="AV3"/>
-      <c r="AW3"/>
-      <c r="AX3"/>
-      <c r="AY3"/>
       <c r="AZ3" s="5"/>
       <c r="BA3" s="5"/>
       <c r="BB3" s="6"/>
@@ -3428,19 +3414,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="2" ht="41.25" customHeight="1" spans="1:5">
@@ -3448,16 +3434,16 @@
         <v>0</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="3" ht="75" customHeight="1" spans="1:5">
@@ -3465,16 +3451,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="4" ht="28" spans="1:5">
@@ -3482,16 +3468,16 @@
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" ht="74.25" customHeight="1" spans="1:5">
@@ -3499,16 +3485,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="6" ht="49.5" customHeight="1" spans="1:5">
@@ -3516,16 +3502,16 @@
         <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="7" ht="49.5" customHeight="1" spans="1:5">
@@ -3533,16 +3519,16 @@
         <v>5</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>5</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="8" ht="28" spans="1:5">
@@ -3550,16 +3536,16 @@
         <v>6</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="9" ht="56" spans="1:5">
@@ -3567,16 +3553,16 @@
         <v>7</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10" ht="56" spans="1:5">
@@ -3584,16 +3570,16 @@
         <v>8</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="11" ht="28" spans="1:5">
@@ -3601,16 +3587,16 @@
         <v>9</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="12" ht="28" spans="1:5">
@@ -3618,16 +3604,16 @@
         <v>10</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="13" ht="28" spans="1:5">
@@ -3635,16 +3621,16 @@
         <v>11</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="14" ht="28" spans="1:5">
@@ -3652,16 +3638,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="15" ht="28" spans="1:5">
@@ -3669,16 +3655,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="16" ht="28" spans="1:5">
@@ -3686,16 +3672,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="17" ht="28" spans="1:5">
@@ -3703,16 +3689,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="18" ht="28" spans="1:5">
@@ -3720,16 +3706,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="19" ht="28" spans="1:5">
@@ -3737,16 +3723,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="20" ht="28" spans="1:5">
@@ -3754,16 +3740,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="21" ht="28" spans="1:5">
@@ -3771,16 +3757,16 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>20</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="22" ht="84" spans="1:5">
@@ -3788,16 +3774,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>21</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="23" ht="28" spans="1:5">
@@ -3805,16 +3791,16 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="24" ht="28" spans="1:5">
@@ -3822,16 +3808,16 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="25" ht="84" spans="1:5">
@@ -3839,16 +3825,16 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>24</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="26" ht="28" spans="1:5">
@@ -3856,16 +3842,16 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="27" ht="28" spans="1:5">
@@ -3873,16 +3859,16 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D27" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="28" ht="28" spans="1:5">
@@ -3890,16 +3876,16 @@
         <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D28" s="7" t="s">
         <v>27</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="29" ht="28" spans="1:5">
@@ -3907,16 +3893,16 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="30" ht="28" spans="1:5">
@@ -3924,16 +3910,16 @@
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="31" ht="28" spans="1:5">
@@ -3941,16 +3927,16 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="32" ht="28" spans="1:5">
@@ -3958,16 +3944,16 @@
         <v>32</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="33" ht="28" spans="1:5">
@@ -3975,16 +3961,16 @@
         <v>33</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="34" ht="28" spans="1:5">
@@ -3992,16 +3978,16 @@
         <v>34</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="35" ht="28" spans="1:5">
@@ -4009,16 +3995,16 @@
         <v>35</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="36" ht="28" spans="1:5">
@@ -4026,16 +4012,16 @@
         <v>36</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="37" ht="28" spans="1:5">
@@ -4043,16 +4029,16 @@
         <v>37</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="38" ht="28" spans="1:5">
@@ -4060,16 +4046,16 @@
         <v>38</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="39" ht="28" spans="1:5">
@@ -4077,16 +4063,16 @@
         <v>39</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>39</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="40" ht="84" spans="1:5">
@@ -4094,16 +4080,16 @@
         <v>40</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>40</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="41" ht="28" spans="1:5">
@@ -4111,16 +4097,16 @@
         <v>42</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="42" ht="84" spans="1:5">
@@ -4128,16 +4114,16 @@
         <v>43</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="43" ht="28" spans="1:5">
@@ -4145,16 +4131,16 @@
         <v>41</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>41</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="44" ht="28" spans="1:5">
@@ -4162,16 +4148,16 @@
         <v>50</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D44" s="4" t="s">
         <v>50</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="45" ht="42" spans="1:5">
@@ -4179,16 +4165,16 @@
         <v>51</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="46" ht="56" spans="1:5">
@@ -4196,16 +4182,16 @@
         <v>52</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="47" ht="42" spans="1:5">
@@ -4213,16 +4199,16 @@
         <v>53</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="48" ht="56" spans="1:5">
@@ -4230,16 +4216,16 @@
         <v>54</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="49" ht="42" spans="1:5">
@@ -4247,16 +4233,16 @@
         <v>55</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="50" ht="56" spans="1:5">
@@ -4264,16 +4250,16 @@
         <v>56</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="51" ht="28" spans="1:5">
@@ -4281,16 +4267,16 @@
         <v>57</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="52" ht="28" spans="1:5">
@@ -4298,16 +4284,16 @@
         <v>58</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="53" ht="28" spans="1:5">
@@ -4315,16 +4301,16 @@
         <v>59</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="54" ht="42" spans="1:5">
@@ -4332,16 +4318,16 @@
         <v>60</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="55" ht="28" spans="1:5">
@@ -4349,16 +4335,16 @@
         <v>61</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="56" ht="28" spans="1:5">
@@ -4366,16 +4352,16 @@
         <v>62</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="57" ht="28" spans="1:5">
@@ -4383,16 +4369,16 @@
         <v>63</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="58" ht="28" spans="1:5">
@@ -4400,16 +4386,16 @@
         <v>64</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D58" s="8" t="s">
         <v>64</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="59" ht="42" spans="1:5">
@@ -4417,16 +4403,16 @@
         <v>65</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="60" ht="42" spans="1:5">
@@ -4434,16 +4420,16 @@
         <v>66</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="61" ht="42" spans="1:5">
@@ -4451,16 +4437,16 @@
         <v>69</v>
       </c>
       <c r="B61" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D61" t="s">
         <v>69</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="62" ht="28" spans="1:5">
@@ -4468,16 +4454,16 @@
         <v>70</v>
       </c>
       <c r="B62" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D62" t="s">
         <v>70</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="63" ht="28" spans="1:5">
@@ -4485,16 +4471,16 @@
         <v>71</v>
       </c>
       <c r="B63" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D63" t="s">
         <v>71</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="64" ht="28" spans="1:5">
@@ -4502,16 +4488,16 @@
         <v>75</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="65" ht="28" spans="1:5">
@@ -4519,16 +4505,16 @@
         <v>76</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="66" ht="28" spans="1:5">
@@ -4536,16 +4522,16 @@
         <v>77</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="67" ht="28" spans="1:5">
@@ -4553,16 +4539,16 @@
         <v>78</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="68" ht="28" spans="1:5">
@@ -4570,16 +4556,16 @@
         <v>79</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="69" ht="28" spans="1:5">
@@ -4587,16 +4573,16 @@
         <v>80</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="70" ht="42" spans="1:5">
@@ -4604,16 +4590,16 @@
         <v>81</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="71" ht="28" spans="1:5">
@@ -4621,16 +4607,16 @@
         <v>82</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="72" ht="28" spans="1:5">
@@ -4638,50 +4624,50 @@
         <v>83</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="73" customFormat="1" ht="42" spans="1:5">
       <c r="A73" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B73" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="74" customFormat="1" ht="28" spans="1:5">
       <c r="A74" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B74" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="75" customFormat="1" ht="42" spans="1:5">
@@ -4689,16 +4675,16 @@
         <v>86</v>
       </c>
       <c r="B75" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="76" customFormat="1" ht="42" spans="1:5">
@@ -4706,16 +4692,16 @@
         <v>87</v>
       </c>
       <c r="B76" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="77" customFormat="1" ht="28" spans="1:5">
@@ -4723,16 +4709,16 @@
         <v>88</v>
       </c>
       <c r="B77" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="78" customFormat="1" spans="1:6">
@@ -4740,14 +4726,14 @@
         <v>89</v>
       </c>
       <c r="B78" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C78" s="4"/>
       <c r="D78" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F78" s="10"/>
     </row>
@@ -4756,16 +4742,16 @@
         <v>90</v>
       </c>
       <c r="B79" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="80" ht="42" spans="1:5">
@@ -4773,16 +4759,16 @@
         <v>91</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D80" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="81" ht="28" spans="1:5">
@@ -4790,16 +4776,16 @@
         <v>92</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D81" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="82" ht="28" spans="1:5">
@@ -4807,16 +4793,16 @@
         <v>93</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="83" ht="28" spans="1:5">
@@ -4824,16 +4810,16 @@
         <v>94</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D83" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="84" ht="28" spans="1:5">
@@ -4841,16 +4827,16 @@
         <v>95</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="85" ht="28" spans="1:5">
@@ -4858,16 +4844,16 @@
         <v>96</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="86" ht="28" spans="1:5">
@@ -4875,16 +4861,16 @@
         <v>97</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="87" ht="28" spans="1:5">
@@ -4892,16 +4878,16 @@
         <v>98</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="88" ht="28" spans="1:5">
@@ -4909,16 +4895,16 @@
         <v>99</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="89" ht="28" spans="1:5">
@@ -4926,16 +4912,16 @@
         <v>100</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="90" ht="28" spans="1:5">
@@ -4943,16 +4929,16 @@
         <v>101</v>
       </c>
       <c r="B90" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="91" ht="28" spans="1:5">
@@ -4960,16 +4946,16 @@
         <v>102</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="92" ht="28" spans="1:5">
@@ -4977,16 +4963,16 @@
         <v>103</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="93" ht="28" spans="1:5">
@@ -4994,16 +4980,16 @@
         <v>104</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="94" ht="28" spans="1:5">
@@ -5011,16 +4997,16 @@
         <v>105</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="95" ht="28" spans="1:5">
@@ -5028,16 +5014,16 @@
         <v>106</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="96" ht="28" spans="1:5">
@@ -5045,16 +5031,16 @@
         <v>107</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="97" ht="28" spans="1:5">
@@ -5062,16 +5048,16 @@
         <v>108</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="98" ht="42" spans="1:5">
@@ -5079,16 +5065,16 @@
         <v>109</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="99" ht="28" spans="1:5">
@@ -5096,16 +5082,16 @@
         <v>110</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="100" ht="28" spans="1:5">
@@ -5113,50 +5099,50 @@
         <v>111</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="101" customFormat="1" ht="42" spans="1:5">
       <c r="A101" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B101" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="102" customFormat="1" ht="28" spans="1:5">
       <c r="A102" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B102" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="103" customFormat="1" ht="42" spans="1:5">
@@ -5164,16 +5150,16 @@
         <v>114</v>
       </c>
       <c r="B103" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="104" customFormat="1" ht="42" spans="1:5">
@@ -5181,16 +5167,16 @@
         <v>115</v>
       </c>
       <c r="B104" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="105" customFormat="1" ht="28" spans="1:5">
@@ -5198,31 +5184,31 @@
         <v>116</v>
       </c>
       <c r="B105" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="106" customFormat="1" spans="1:6">
       <c r="A106" s="8" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B106" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C106" s="4"/>
       <c r="D106" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F106" s="10"/>
     </row>
@@ -5231,16 +5217,16 @@
         <v>118</v>
       </c>
       <c r="B107" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="108" ht="42" spans="1:5">
@@ -5248,16 +5234,16 @@
         <v>119</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D108" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="109" ht="28" spans="1:5">
@@ -5265,16 +5251,16 @@
         <v>120</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D109" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="110" ht="28" spans="1:5">
@@ -5282,16 +5268,16 @@
         <v>121</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="111" ht="28" spans="1:5">
@@ -5299,16 +5285,16 @@
         <v>122</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D111" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="112" ht="28" spans="1:5">
@@ -5316,16 +5302,16 @@
         <v>123</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="113" ht="28" spans="1:5">
@@ -5333,16 +5319,16 @@
         <v>124</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="114" ht="28" spans="1:5">
@@ -5350,16 +5336,16 @@
         <v>125</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="115" ht="28" spans="1:5">
@@ -5367,16 +5353,16 @@
         <v>126</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="116" ht="28" spans="1:5">
@@ -5384,16 +5370,16 @@
         <v>127</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="117" ht="28" spans="1:5">
@@ -5401,16 +5387,16 @@
         <v>128</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="118" ht="28" spans="1:5">
@@ -5418,16 +5404,16 @@
         <v>129</v>
       </c>
       <c r="B118" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="120" ht="28" spans="1:5">
@@ -5435,21 +5421,21 @@
         <v>130</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="122" ht="56" spans="1:1">
       <c r="A122" s="4" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
   </sheetData>
@@ -5470,410 +5456,410 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
   </sheetData>
